--- a/Pinterest-Distribution-Plan.xlsx
+++ b/Pinterest-Distribution-Plan.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="404">
   <si>
     <t xml:space="preserve">Pinterest Distribution Strategy - travelsamericas.com</t>
   </si>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">Itinerary and "solo-friendly spots" pins</t>
   </si>
   <si>
-    <t xml:space="preserve">"Solo Trip to NYC: The 4-Day Itinerary That Actually Works Alone" / "13 Things to Do Alone in NYC (That Don't Feel Lonely)" / "Eating Alone in NYC Without the Awkwardness"</t>
+    <t xml:space="preserve">"Solo Trip to NYC: The 3-Day Itinerary That Actually Works Alone" / "13 Things to Do Alone in NYC (That Don't Feel Lonely)" / "Eating Alone in NYC Without the Awkwardness"</t>
   </si>
   <si>
     <t xml:space="preserve">"Alone without lonely" framing tests well in this vertical</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">Packing list, pre-trip setup, app list pins</t>
   </si>
   <si>
-    <t xml:space="preserve">"Pre-Trip Safety Setup: 7 Things to Do Before You Land in NYC" / "Free 4-Day NYC Solo Itinerary (Printable PDF)"</t>
+    <t xml:space="preserve">"Pre-Trip Safety Setup: 7 Things to Do Before You Land in NYC" / "Free 3-Day NYC Solo Itinerary (Printable PDF)"</t>
   </si>
   <si>
     <t xml:space="preserve">PDF pins link straight to the email capture</t>
@@ -464,6 +464,9 @@
     <t xml:space="preserve">When</t>
   </si>
   <si>
+    <t xml:space="preserve">Status (Jun 10)</t>
+  </si>
+  <si>
     <t xml:space="preserve">BLOCKERS - DO BEFORE FIRST PIN</t>
   </si>
   <si>
@@ -479,6 +482,9 @@
     <t xml:space="preserve">Export your existing solo-itinerary page content into a designed 8-12 page PDF</t>
   </si>
   <si>
+    <t xml:space="preserve">NOT STARTED — top blocker</t>
+  </si>
+  <si>
     <t xml:space="preserve">2</t>
   </si>
   <si>
@@ -488,12 +494,15 @@
     <t xml:space="preserve">Pages pins link to (safety guide, solo trip, female solo, best areas, itinerary) must capture emails on first screen, not just footer</t>
   </si>
   <si>
-    <t xml:space="preserve">Inline form: "Get the free 4-day solo NYC itinerary (PDF)" + first-name/email</t>
+    <t xml:space="preserve">Inline form: "Get the free 3-day solo NYC itinerary (PDF)" + first-name/email</t>
   </si>
   <si>
     <t xml:space="preserve">Week 1-2</t>
   </si>
   <si>
+    <t xml:space="preserve">Not started</t>
+  </si>
+  <si>
     <t xml:space="preserve">3</t>
   </si>
   <si>
@@ -524,6 +533,9 @@
     <t xml:space="preserve">Week 2-3</t>
   </si>
   <si>
+    <t xml:space="preserve">Partially mitigated: 10 OG share cards built (in code, NOT deployed). Vertical 1000x1500 pin images still needed</t>
+  </si>
+  <si>
     <t xml:space="preserve">5</t>
   </si>
   <si>
@@ -551,6 +563,9 @@
     <t xml:space="preserve">developers.pinterest.com validator, one-time</t>
   </si>
   <si>
+    <t xml:space="preserve">DONE — claim verified; validator retired, Rich Pins auto-apply</t>
+  </si>
+  <si>
     <t xml:space="preserve">TEXT - LANDING PAGE ALIGNMENT</t>
   </si>
   <si>
@@ -659,6 +674,9 @@
     <t xml:space="preserve">Quality bar / notes</t>
   </si>
   <si>
+    <t xml:space="preserve">Status (as of Jun 10, 2026)</t>
+  </si>
+  <si>
     <t xml:space="preserve">PHASE 1: FOUNDATION (Weeks 1-2)</t>
   </si>
   <si>
@@ -677,13 +695,16 @@
     <t xml:space="preserve">Test: pin URL -&gt; page -&gt; signup -&gt; email lands with working PDF link</t>
   </si>
   <si>
+    <t xml:space="preserve">PARTIAL. Done: business account, domain claimed+verified, Rich Pin metadata (og:type=article on ~50 pages, OG blocks on 7 NYC pages, title bugfix, 10 OG cards w/ logo+Bold font). NOT DONE: deploy of OG work, PDF lead magnet, SafetyWing/Airalo applications, homepage thumbnail fix, UTM scheme. Carry-overs move to Week 2.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Boards + design system</t>
   </si>
   <si>
     <t xml:space="preserve">Create 8 boards (see Pin Formats sheet for names/keywords). Hire Fiverr designer with the brief OR build 6 Canva master templates yourself. Generate AI background batch (10 illustrated images). Add email capture to top 5 pages.</t>
   </si>
   <si>
-    <t xml:space="preserve">You 2 hrs + designer ($60-150)</t>
+    <t xml:space="preserve">You 2 hrs + AI agent (designer line item removed)</t>
   </si>
   <si>
     <t xml:space="preserve">8 keyword-named boards; 6 approved master templates</t>
@@ -692,6 +713,9 @@
     <t xml:space="preserve">Templates must pass the squint test: title readable at thumbnail size on mobile</t>
   </si>
   <si>
+    <t xml:space="preserve">STARTS MON JUN 15. Revised: AI agent replaces Fiverr designer for all graphics (decision Jun 10). Must-do this week: DEPLOY pending OG/article changes; ship PDF; apply to affiliate programs; create 8 boards (copy ready); finish profile (avatar+bio+email confirm); 6 pin master templates via agent WITH visual QA gate.</t>
+  </si>
+  <si>
     <t xml:space="preserve">PHASE 2: PRODUCTION RAMP (Weeks 3-5)</t>
   </si>
   <si>
@@ -710,6 +734,9 @@
     <t xml:space="preserve">Each pin: unique title, 3-5 keywords in description, UTM link</t>
   </si>
   <si>
+    <t xml:space="preserve">Pending</t>
+  </si>
+  <si>
     <t xml:space="preserve">Batch 2 - 12 pins + baseline</t>
   </si>
   <si>
@@ -896,7 +923,7 @@
     <t xml:space="preserve">FORMAT 4: ITINERARY/DAY-PLANNER PIN (15%)</t>
   </si>
   <si>
-    <t xml:space="preserve">1000x1500. "4 Days in NYC Solo" - vertical timeline Day 1-4 with one line each, PDF CTA at bottom.</t>
+    <t xml:space="preserve">1000x1500. "3 Days in NYC Solo" - vertical timeline Day 1-3 with one line each, PDF CTA at bottom.</t>
   </si>
   <si>
     <t xml:space="preserve">Direct feeder to email capture</t>
@@ -1052,6 +1079,57 @@
     <t xml:space="preserve">&lt;10k impressions AND &lt;20 subs -&gt; diagnose funnel stage before adding volume</t>
   </si>
   <si>
+    <t xml:space="preserve">UTM RULE — apply to every pin link, from pin #1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Format</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.travelsamericas.com/&lt;page-path&gt;?utm_source=pinterest&amp;utm_medium=organic&amp;utm_campaign=&lt;pillar&gt;&amp;utm_content=&lt;pin-id&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">utm_source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Always exactly: pinterest (lowercase)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">utm_medium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Always exactly: organic (switch to paid only if ads are ever tested)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">utm_campaign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The messaging pillar, one of: safety / solo / insider / planning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">utm_content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unique pin ID: &lt;format&gt;-&lt;number&gt;, e.g. checklist-01, map-03, listicle-12. Log the ID in your pin tracking so GA4 rows map back to a specific pin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.travelsamericas.com/destination/nyc/solo-itinerary?utm_source=pinterest&amp;utm_medium=organic&amp;utm_campaign=planning&amp;utm_content=itinerary-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where to read results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GA4 -&gt; Reports -&gt; Acquisition -&gt; Traffic acquisition, filter session source = pinterest; add secondary dimension session campaign or session manual ad content. Email signups by pin = key event filtered the same way</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why day one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GA4 cannot attribute retroactively — pins published without UTMs are permanently invisible in attribution. Never edit a live pin URL later; re-pin with the correct link instead</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tool Stack &amp; Budget (automation-first)</t>
   </si>
   <si>
@@ -1091,13 +1169,13 @@
     <t xml:space="preserve">Yes - the automation backbone</t>
   </si>
   <si>
-    <t xml:space="preserve">Fiverr/Upwork designer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$60-150 setup, then $30-60/mo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 master templates, then weekly batch fills (12-15 pins) from your copy doc</t>
+    <t xml:space="preserve">AI agent (replaces Fiverr designer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$0 incremental</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generates templates/cards from prompts with explicit asset values (fonts, hex, logo URL) + STOP-and-report rules. QUALITY GATE REQUIRED: every batch visually reviewed before deploy — 2 of first 3 outputs needed rework (wrong font, thin weight). Fiverr designer remains the fallback at Week 6 review if pin save-rate underperforms.</t>
   </si>
   <si>
     <t xml:space="preserve">Yes per your outsource preference - OR skip and use Canva bulk-create yourself</t>
@@ -1154,10 +1232,10 @@
     <t xml:space="preserve">TOTAL monthly run-rate</t>
   </si>
   <si>
-    <t xml:space="preserve">~$45-100/mo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canva + designer batches + optional Ideogram</t>
+    <t xml:space="preserve">~$15-25/mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canva Pro + optional Ideogram; designer cost removed while AI-agent route holds</t>
   </si>
   <si>
     <t xml:space="preserve">At 50-60 pins/month = $1-2 per pin all-in</t>
@@ -1240,7 +1318,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1256,7 +1334,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDCE9ED"/>
-        <bgColor rgb="FFF4F8FA"/>
+        <bgColor rgb="FFD6EFD6"/>
       </patternFill>
     </fill>
     <fill>
@@ -1267,8 +1345,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFBDADA"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
         <bgColor rgb="FFF4F8FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EFD6"/>
+        <bgColor rgb="FFDCE9ED"/>
       </patternFill>
     </fill>
   </fills>
@@ -1321,12 +1411,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1346,59 +1440,83 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1406,12 +1524,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1459,12 +1581,12 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFF4F8FA"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFD6EFD6"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFFBDADA"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -1669,206 +1791,206 @@
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="70"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="52"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+    <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
+    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+    <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1891,258 +2013,258 @@
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="38"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+    <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+    <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="6" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="6" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="5" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="5" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+    </row>
+    <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="5" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
+    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="6" t="s">
         <v>89</v>
       </c>
     </row>
@@ -2165,203 +2287,203 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="42"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+    <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+    <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+    <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="6" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="5" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="5" t="s">
         <v>138</v>
       </c>
     </row>
@@ -2381,276 +2503,316 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="34"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="D4" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="F4" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="C5" s="5" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="E5" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="F5" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D6" s="4" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="B6" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-    </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="F6" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="F8" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="E9" s="5" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="B9" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C9" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D9" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E9" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F9" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-    </row>
-    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="F10" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="E12" s="4" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B12" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D12" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="E12" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="F12" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="B13" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="C13" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+      <c r="D13" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="E13" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E14" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="B18" s="4" t="s">
+      <c r="F16" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="B17" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="C17" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="D17" s="6" t="s">
         <v>201</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -2669,330 +2831,370 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="46"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="B19" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>235</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -3017,232 +3219,232 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="56"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="D6" s="4" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="D6" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="B12" s="4" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="D8" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="B14" s="4" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+      <c r="D10" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="B16" s="4" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+      <c r="D12" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D14" s="5" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="D19" s="5" t="s">
+    <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="C20" s="4" t="s">
+    <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="5" t="s">
         <v>89</v>
       </c>
     </row>
@@ -3262,513 +3464,663 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="40"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F3" s="2" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="G3" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="10" t="n">
+      <c r="B4" s="13"/>
+      <c r="C4" s="14" t="n">
         <f aca="false">B4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="11" t="str">
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="15" t="str">
         <f aca="false">IF(OR(D4="",D4=0),"-",F4/D4)</f>
         <v>-</v>
       </c>
-      <c r="H4" s="9"/>
-      <c r="I4" s="10" t="n">
+      <c r="H4" s="13"/>
+      <c r="I4" s="14" t="n">
         <f aca="false">H4</f>
         <v>0</v>
       </c>
-      <c r="J4" s="11" t="str">
+      <c r="J4" s="15" t="str">
         <f aca="false">IF(OR(D4="",D4=0),"-",E4/D4)</f>
         <v>-</v>
       </c>
-      <c r="K4" s="12"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="14" t="n">
+      <c r="K4" s="16"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="B5" s="13"/>
+      <c r="C5" s="18" t="n">
         <f aca="false">C4+B5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="15" t="str">
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="19" t="str">
         <f aca="false">IF(OR(D5="",D5=0),"-",F5/D5)</f>
         <v>-</v>
       </c>
-      <c r="H5" s="9"/>
-      <c r="I5" s="14" t="n">
+      <c r="H5" s="13"/>
+      <c r="I5" s="18" t="n">
         <f aca="false">I4+H5</f>
         <v>0</v>
       </c>
-      <c r="J5" s="15" t="str">
+      <c r="J5" s="19" t="str">
         <f aca="false">IF(OR(D5="",D5=0),"-",E5/D5)</f>
         <v>-</v>
       </c>
-      <c r="K5" s="16"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="10" t="n">
+      <c r="K5" s="20"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="B6" s="13"/>
+      <c r="C6" s="14" t="n">
         <f aca="false">C5+B6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="11" t="str">
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="15" t="str">
         <f aca="false">IF(OR(D6="",D6=0),"-",F6/D6)</f>
         <v>-</v>
       </c>
-      <c r="H6" s="9"/>
-      <c r="I6" s="10" t="n">
+      <c r="H6" s="13"/>
+      <c r="I6" s="14" t="n">
         <f aca="false">I5+H6</f>
         <v>0</v>
       </c>
-      <c r="J6" s="11" t="str">
+      <c r="J6" s="15" t="str">
         <f aca="false">IF(OR(D6="",D6=0),"-",E6/D6)</f>
         <v>-</v>
       </c>
-      <c r="K6" s="12"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="14" t="n">
+      <c r="K6" s="16"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="B7" s="13"/>
+      <c r="C7" s="18" t="n">
         <f aca="false">C6+B7</f>
         <v>0</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="15" t="str">
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="19" t="str">
         <f aca="false">IF(OR(D7="",D7=0),"-",F7/D7)</f>
         <v>-</v>
       </c>
-      <c r="H7" s="9"/>
-      <c r="I7" s="14" t="n">
+      <c r="H7" s="13"/>
+      <c r="I7" s="18" t="n">
         <f aca="false">I6+H7</f>
         <v>0</v>
       </c>
-      <c r="J7" s="15" t="str">
+      <c r="J7" s="19" t="str">
         <f aca="false">IF(OR(D7="",D7=0),"-",E7/D7)</f>
         <v>-</v>
       </c>
-      <c r="K7" s="16"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="10" t="n">
+      <c r="K7" s="20"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="B8" s="13"/>
+      <c r="C8" s="14" t="n">
         <f aca="false">C7+B8</f>
         <v>0</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="11" t="str">
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="15" t="str">
         <f aca="false">IF(OR(D8="",D8=0),"-",F8/D8)</f>
         <v>-</v>
       </c>
-      <c r="H8" s="9"/>
-      <c r="I8" s="10" t="n">
+      <c r="H8" s="13"/>
+      <c r="I8" s="14" t="n">
         <f aca="false">I7+H8</f>
         <v>0</v>
       </c>
-      <c r="J8" s="11" t="str">
+      <c r="J8" s="15" t="str">
         <f aca="false">IF(OR(D8="",D8=0),"-",E8/D8)</f>
         <v>-</v>
       </c>
-      <c r="K8" s="12"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
-        <v>322</v>
-      </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="14" t="n">
+      <c r="K8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="B9" s="13"/>
+      <c r="C9" s="18" t="n">
         <f aca="false">C8+B9</f>
         <v>0</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="15" t="str">
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="19" t="str">
         <f aca="false">IF(OR(D9="",D9=0),"-",F9/D9)</f>
         <v>-</v>
       </c>
-      <c r="H9" s="9"/>
-      <c r="I9" s="14" t="n">
+      <c r="H9" s="13"/>
+      <c r="I9" s="18" t="n">
         <f aca="false">I8+H9</f>
         <v>0</v>
       </c>
-      <c r="J9" s="15" t="str">
+      <c r="J9" s="19" t="str">
         <f aca="false">IF(OR(D9="",D9=0),"-",E9/D9)</f>
         <v>-</v>
       </c>
-      <c r="K9" s="16"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="10" t="n">
+      <c r="K9" s="20"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="B10" s="13"/>
+      <c r="C10" s="14" t="n">
         <f aca="false">C9+B10</f>
         <v>0</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="11" t="str">
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="15" t="str">
         <f aca="false">IF(OR(D10="",D10=0),"-",F10/D10)</f>
         <v>-</v>
       </c>
-      <c r="H10" s="9"/>
-      <c r="I10" s="10" t="n">
+      <c r="H10" s="13"/>
+      <c r="I10" s="14" t="n">
         <f aca="false">I9+H10</f>
         <v>0</v>
       </c>
-      <c r="J10" s="11" t="str">
+      <c r="J10" s="15" t="str">
         <f aca="false">IF(OR(D10="",D10=0),"-",E10/D10)</f>
         <v>-</v>
       </c>
-      <c r="K10" s="12"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
-        <v>324</v>
-      </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="14" t="n">
+      <c r="K10" s="16"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="17" t="s">
+        <v>333</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="18" t="n">
         <f aca="false">C10+B11</f>
         <v>0</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="15" t="str">
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="19" t="str">
         <f aca="false">IF(OR(D11="",D11=0),"-",F11/D11)</f>
         <v>-</v>
       </c>
-      <c r="H11" s="9"/>
-      <c r="I11" s="14" t="n">
+      <c r="H11" s="13"/>
+      <c r="I11" s="18" t="n">
         <f aca="false">I10+H11</f>
         <v>0</v>
       </c>
-      <c r="J11" s="15" t="str">
+      <c r="J11" s="19" t="str">
         <f aca="false">IF(OR(D11="",D11=0),"-",E11/D11)</f>
         <v>-</v>
       </c>
-      <c r="K11" s="16"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="10" t="n">
+      <c r="K11" s="20"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14" t="n">
         <f aca="false">C11+B12</f>
         <v>0</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="11" t="str">
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="15" t="str">
         <f aca="false">IF(OR(D12="",D12=0),"-",F12/D12)</f>
         <v>-</v>
       </c>
-      <c r="H12" s="9"/>
-      <c r="I12" s="10" t="n">
+      <c r="H12" s="13"/>
+      <c r="I12" s="14" t="n">
         <f aca="false">I11+H12</f>
         <v>0</v>
       </c>
-      <c r="J12" s="11" t="str">
+      <c r="J12" s="15" t="str">
         <f aca="false">IF(OR(D12="",D12=0),"-",E12/D12)</f>
         <v>-</v>
       </c>
-      <c r="K12" s="12"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
-        <v>326</v>
-      </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="14" t="n">
+      <c r="K12" s="16"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="B13" s="13"/>
+      <c r="C13" s="18" t="n">
         <f aca="false">C12+B13</f>
         <v>0</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="15" t="str">
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="19" t="str">
         <f aca="false">IF(OR(D13="",D13=0),"-",F13/D13)</f>
         <v>-</v>
       </c>
-      <c r="H13" s="9"/>
-      <c r="I13" s="14" t="n">
+      <c r="H13" s="13"/>
+      <c r="I13" s="18" t="n">
         <f aca="false">I12+H13</f>
         <v>0</v>
       </c>
-      <c r="J13" s="15" t="str">
+      <c r="J13" s="19" t="str">
         <f aca="false">IF(OR(D13="",D13=0),"-",E13/D13)</f>
         <v>-</v>
       </c>
-      <c r="K13" s="16"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="10" t="n">
+      <c r="K13" s="20"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="14" t="n">
         <f aca="false">C13+B14</f>
         <v>0</v>
       </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="11" t="str">
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="15" t="str">
         <f aca="false">IF(OR(D14="",D14=0),"-",F14/D14)</f>
         <v>-</v>
       </c>
-      <c r="H14" s="9"/>
-      <c r="I14" s="10" t="n">
+      <c r="H14" s="13"/>
+      <c r="I14" s="14" t="n">
         <f aca="false">I13+H14</f>
         <v>0</v>
       </c>
-      <c r="J14" s="11" t="str">
+      <c r="J14" s="15" t="str">
         <f aca="false">IF(OR(D14="",D14=0),"-",E14/D14)</f>
         <v>-</v>
       </c>
-      <c r="K14" s="12"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
-        <v>328</v>
-      </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="14" t="n">
+      <c r="K14" s="16"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="18" t="n">
         <f aca="false">C14+B15</f>
         <v>0</v>
       </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="15" t="str">
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="19" t="str">
         <f aca="false">IF(OR(D15="",D15=0),"-",F15/D15)</f>
         <v>-</v>
       </c>
-      <c r="H15" s="9"/>
-      <c r="I15" s="14" t="n">
+      <c r="H15" s="13"/>
+      <c r="I15" s="18" t="n">
         <f aca="false">I14+H15</f>
         <v>0</v>
       </c>
-      <c r="J15" s="15" t="str">
+      <c r="J15" s="19" t="str">
         <f aca="false">IF(OR(D15="",D15=0),"-",E15/D15)</f>
         <v>-</v>
       </c>
-      <c r="K15" s="16"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17" t="s">
-        <v>329</v>
-      </c>
-      <c r="B16" s="17" t="n">
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="s">
+        <v>338</v>
+      </c>
+      <c r="B16" s="21" t="n">
         <f aca="false">SUM(B4:B15)</f>
         <v>0</v>
       </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="17" t="n">
+      <c r="C16" s="22"/>
+      <c r="D16" s="21" t="n">
         <f aca="false">SUM(D4:D15)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="17" t="n">
+      <c r="E16" s="21" t="n">
         <f aca="false">SUM(E4:E15)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="17" t="n">
+      <c r="F16" s="21" t="n">
         <f aca="false">SUM(F4:F15)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="19" t="str">
+      <c r="G16" s="23" t="str">
         <f aca="false">IF(D16=0,"-",F16/D16)</f>
         <v>-</v>
       </c>
-      <c r="H16" s="17" t="n">
+      <c r="H16" s="21" t="n">
         <f aca="false">SUM(H4:H15)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="18"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="20" t="s">
-        <v>330</v>
-      </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="24" t="s">
+        <v>339</v>
+      </c>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="22" t="s">
-        <v>331</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>332</v>
-      </c>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+      <c r="A19" s="26" t="s">
+        <v>340</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>341</v>
+      </c>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="22" t="s">
-        <v>333</v>
-      </c>
-      <c r="B20" s="21" t="s">
-        <v>334</v>
-      </c>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
+      <c r="A20" s="26" t="s">
+        <v>342</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>343</v>
+      </c>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="22" t="s">
-        <v>335</v>
-      </c>
-      <c r="B21" s="21" t="s">
-        <v>336</v>
-      </c>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
+      <c r="A21" s="26" t="s">
+        <v>344</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>345</v>
+      </c>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="B22" s="21" t="s">
-        <v>338</v>
-      </c>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
+      <c r="A22" s="26" t="s">
+        <v>346</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>347</v>
+      </c>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="22" t="s">
-        <v>339</v>
-      </c>
-      <c r="B23" s="21" t="s">
-        <v>340</v>
-      </c>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
+      <c r="A23" s="26" t="s">
+        <v>348</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>349</v>
+      </c>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="27" t="s">
+        <v>350</v>
+      </c>
+      <c r="B25" s="28"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="29" t="s">
+        <v>351</v>
+      </c>
+      <c r="B26" s="25" t="s">
+        <v>352</v>
+      </c>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="25"/>
+      <c r="K26" s="25"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="29" t="s">
+        <v>353</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>354</v>
+      </c>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="25"/>
+      <c r="K27" s="25"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="29" t="s">
+        <v>355</v>
+      </c>
+      <c r="B28" s="25" t="s">
+        <v>356</v>
+      </c>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="25"/>
+      <c r="K28" s="25"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="29" t="s">
+        <v>357</v>
+      </c>
+      <c r="B29" s="25" t="s">
+        <v>358</v>
+      </c>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="25"/>
+      <c r="K29" s="25"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="29" t="s">
+        <v>359</v>
+      </c>
+      <c r="B30" s="25" t="s">
+        <v>360</v>
+      </c>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="25"/>
+      <c r="K30" s="25"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="29" t="s">
+        <v>361</v>
+      </c>
+      <c r="B31" s="25" t="s">
+        <v>362</v>
+      </c>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="25"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="25"/>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="29" t="s">
+        <v>363</v>
+      </c>
+      <c r="B32" s="25" t="s">
+        <v>364</v>
+      </c>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="25"/>
+      <c r="J32" s="25"/>
+      <c r="K32" s="25"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="29" t="s">
+        <v>365</v>
+      </c>
+      <c r="B33" s="25" t="s">
+        <v>366</v>
+      </c>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="25"/>
+      <c r="K33" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="14">
     <mergeCell ref="B18:H18"/>
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="B20:H20"/>
     <mergeCell ref="B21:H21"/>
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="B23:H23"/>
+    <mergeCell ref="B26:K26"/>
+    <mergeCell ref="B27:K27"/>
+    <mergeCell ref="B28:K28"/>
+    <mergeCell ref="B29:K29"/>
+    <mergeCell ref="B30:K30"/>
+    <mergeCell ref="B31:K31"/>
+    <mergeCell ref="B32:K32"/>
+    <mergeCell ref="B33:K33"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3788,169 +4140,169 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="34"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="D2" s="2" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="E2" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="E9" s="5" t="s">
+      <c r="E3" s="6" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="C8" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>401</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>402</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>377</v>
+      <c r="E10" s="4" t="s">
+        <v>403</v>
       </c>
     </row>
   </sheetData>

--- a/Pinterest-Distribution-Plan.xlsx
+++ b/Pinterest-Distribution-Plan.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Pin Formats + AI Prompts" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Scorecard" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="Tools &amp; Budget" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Pin Batch 1" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="472">
   <si>
     <t xml:space="preserve">Pinterest Distribution Strategy - travelsamericas.com</t>
   </si>
@@ -1239,6 +1240,210 @@
   </si>
   <si>
     <t xml:space="preserve">At 50-60 pins/month = $1-2 per pin all-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pin Batch 1 — Week 3 (12 pins, schedule 2/day)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workflow per pin: open template SVG -&gt; replace placeholders with Title (split across the two title lines) -&gt; export PNG 1000x1500 -&gt; upload to Pinterest -&gt; paste Title, Description, URL exactly -&gt; assign Board -&gt; schedule. Mark Status when queued.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pin ID (utm_content)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Board</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pin Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pin Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destination URL (paste exactly)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">checklist-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Checklist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYC Safety Tips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYC Safety Checklist: 7 Habits for First-Time Visitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practical NYC safety tips for tourists — subway habits, scam awareness, and smart night-walking rules from a street-tested New York City safety guide. Save this checklist for your trip.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.travelsamericas.com/destination/nyc/nyc-safety-guide?utm_source=pinterest&amp;utm_medium=organic&amp;utm_campaign=safety&amp;utm_content=checklist-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">checklist-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYC Subway + Getting Around</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYC Subway at Night: 5 Rules I Always Follow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riding the NYC subway alone at night? These 5 subway safety rules — where to stand, which car to pick, late-night transfer tips — keep solo travelers confident.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.travelsamericas.com/destination/nyc/subway-safety-guide?utm_source=pinterest&amp;utm_medium=organic&amp;utm_campaign=safety&amp;utm_content=checklist-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">checklist-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYC Solo Female Travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo Female Travel NYC: Pre-Trip Safety Setup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traveling to New York alone? 5 things to set up before you land — location sharing, backup payments, and the safety apps worth having. From our NYC solo female travel guide.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.travelsamericas.com/destination/nyc/nyc-female-solo-travel-guide?utm_source=pinterest&amp;utm_medium=organic&amp;utm_campaign=safety&amp;utm_content=checklist-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">checklist-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is NYC Safe at Night? 5 Things to Know</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walking NYC at night as a tourist: which areas stay busy, when to switch to rideshare, and the after-dark rules locals actually use. Honest night-safety breakdown.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.travelsamericas.com/destination/nyc/is-nyc-safe-at-night?utm_source=pinterest&amp;utm_medium=organic&amp;utm_campaign=safety&amp;utm_content=checklist-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">itinerary-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Itinerary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYC Itineraries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 Days in NYC Alone: An Itinerary That Works</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A realistic 3-day NYC itinerary for solo travelers — Central Park to the Brooklyn Bridge, with solo-friendly food stops and budget notes. Free printable PDF included.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.travelsamericas.com/destination/nyc/solo-itinerary?utm_source=pinterest&amp;utm_medium=organic&amp;utm_campaign=planning&amp;utm_content=itinerary-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">itinerary-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo Trip to NYC: The First-Timer’s Plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planning a solo trip to New York City? Where to stay, how to ride the subway with confidence, daily budgets, and a 3-day plan — built for first-time solo travelers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.travelsamericas.com/destination/nyc/solo-trip-to-nyc?utm_source=pinterest&amp;utm_medium=organic&amp;utm_campaign=solo&amp;utm_content=itinerary-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">itinerary-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your First 24 Hours in NYC, Solo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The arrival-day plan that prevents day-one burnout: transit from JFK, a 30-minute orientation loop, and the easiest first solo dinner in New York City.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.travelsamericas.com/destination/nyc/solo-trip-to-nyc?utm_source=pinterest&amp;utm_medium=organic&amp;utm_campaign=solo&amp;utm_content=itinerary-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">listicle-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Listicle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where to Stay in NYC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 Safest Areas to Stay in NYC, Compared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where to stay in NYC as a solo traveler: 7 neighborhoods compared for safety, late-night walkability, and subway access — with the hotel zones worth paying for.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.travelsamericas.com/destination/nyc/best-areas-to-stay?utm_source=pinterest&amp;utm_medium=organic&amp;utm_campaign=insider&amp;utm_content=listicle-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">map-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 Map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYC After Dark: Walk Here, Ride There</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An honest NYC neighborhood safety map for visitors — where streets stay lively at night, where to stay alert, and where a rideshare beats walking. Block-by-block guide.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.travelsamericas.com/destination/nyc/neighborhood-guide?utm_source=pinterest&amp;utm_medium=organic&amp;utm_campaign=insider&amp;utm_content=map-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">listicle-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where to Stay in NYC: First Solo Trip Edition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First solo trip to New York? Stay between 14th and 96th in Manhattan, within 5 minutes of a subway line — plus 3 rules for picking a safe hotel block.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.travelsamericas.com/destination/nyc/best-areas-to-stay?utm_source=pinterest&amp;utm_medium=organic&amp;utm_campaign=insider&amp;utm_content=listicle-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free PDF: 3-Day NYC Solo Itinerary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grab the free printable NYC itinerary — day-by-day plan, packing list, and budget breakdown, sent instantly. Made for first-time solo travelers to New York City.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.travelsamericas.com/destination/nyc/solo-itinerary?utm_source=pinterest&amp;utm_medium=organic&amp;utm_campaign=planning&amp;utm_content=pdf-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 Stat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo Travel Tips for Women</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYC Packing List + 3-Day Plan (Free PDF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to pack for New York plus a complete 3-day solo plan in one free PDF — walking-shoe rules, subway payment tips, and a realistic budget table. Sent instantly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.travelsamericas.com/destination/nyc/solo-itinerary?utm_source=pinterest&amp;utm_medium=organic&amp;utm_campaign=planning&amp;utm_content=pdf-02</t>
   </si>
 </sst>
 </file>
@@ -1411,7 +1616,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1520,20 +1725,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -3963,14 +4164,14 @@
       <c r="G23" s="25"/>
       <c r="H23" s="25"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="27" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="24" t="s">
         <v>350</v>
       </c>
-      <c r="B25" s="28"/>
+      <c r="B25" s="27"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="29" t="s">
+      <c r="A26" s="26" t="s">
         <v>351</v>
       </c>
       <c r="B26" s="25" t="s">
@@ -3987,7 +4188,7 @@
       <c r="K26" s="25"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="29" t="s">
+      <c r="A27" s="26" t="s">
         <v>353</v>
       </c>
       <c r="B27" s="25" t="s">
@@ -4004,7 +4205,7 @@
       <c r="K27" s="25"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="26" t="s">
         <v>355</v>
       </c>
       <c r="B28" s="25" t="s">
@@ -4021,7 +4222,7 @@
       <c r="K28" s="25"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="29" t="s">
+      <c r="A29" s="26" t="s">
         <v>357</v>
       </c>
       <c r="B29" s="25" t="s">
@@ -4038,7 +4239,7 @@
       <c r="K29" s="25"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="29" t="s">
+      <c r="A30" s="26" t="s">
         <v>359</v>
       </c>
       <c r="B30" s="25" t="s">
@@ -4055,7 +4256,7 @@
       <c r="K30" s="25"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="29" t="s">
+      <c r="A31" s="26" t="s">
         <v>361</v>
       </c>
       <c r="B31" s="25" t="s">
@@ -4071,8 +4272,8 @@
       <c r="J31" s="25"/>
       <c r="K31" s="25"/>
     </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="29" t="s">
+    <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="26" t="s">
         <v>363</v>
       </c>
       <c r="B32" s="25" t="s">
@@ -4089,7 +4290,7 @@
       <c r="K32" s="25"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="29" t="s">
+      <c r="A33" s="26" t="s">
         <v>365</v>
       </c>
       <c r="B33" s="25" t="s">
@@ -4292,10 +4493,10 @@
       <c r="A10" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="28" t="s">
         <v>401</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="28" t="s">
         <v>402</v>
       </c>
       <c r="D10" s="4" t="s">
@@ -4314,4 +4515,367 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="29" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+    </row>
+    <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="H4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="H6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="H7" s="5"/>
+    </row>
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="H9" s="5"/>
+    </row>
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="H10" s="6"/>
+    </row>
+    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="H12" s="6"/>
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="H13" s="5"/>
+    </row>
+    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="H14" s="6"/>
+    </row>
+    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="H15" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>